--- a/data-visualization/power-bi/examples/sorting-tables/data2/prod_db.xlsx
+++ b/data-visualization/power-bi/examples/sorting-tables/data2/prod_db.xlsx
@@ -8,7 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="fruits_db" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="fruits_db2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,17 +21,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
-  <si>
-    <t xml:space="preserve">Quality Index</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="18">
+  <si>
+    <t xml:space="preserve">Fruit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flavor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freshnesh</t>
   </si>
   <si>
     <t xml:space="preserve">Apple1</t>
   </si>
   <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passed</t>
+  </si>
+  <si>
     <t xml:space="preserve">Apple2</t>
   </si>
   <si>
+    <t xml:space="preserve">Not Passed</t>
+  </si>
+  <si>
     <t xml:space="preserve">Apple3</t>
   </si>
   <si>
@@ -49,28 +71,10 @@
     <t xml:space="preserve">Percentage</t>
   </si>
   <si>
+    <t xml:space="preserve">Percentage Overall</t>
+  </si>
+  <si>
     <t xml:space="preserve">Date Update</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not Passed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flavor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freshnesh</t>
   </si>
 </sst>
 </file>
@@ -349,11 +353,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="12.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.6"/>
@@ -377,149 +382,194 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
+      <c r="H1" s="0"/>
+      <c r="I1" s="0"/>
+      <c r="J1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>46023</v>
-      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
+      <c r="I2" s="0"/>
+      <c r="J2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>46024</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+      <c r="I3" s="0"/>
+      <c r="J3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>46025</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+      <c r="I4" s="0"/>
+      <c r="J4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+      <c r="I5" s="0"/>
+      <c r="J5" s="0"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="B7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>46026</v>
-      </c>
+      <c r="B8" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0"/>
+      <c r="D11" s="0"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0"/>
+      <c r="D12" s="0"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0"/>
+      <c r="D13" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0"/>
+      <c r="D14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0"/>
+      <c r="D15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0"/>
+      <c r="D16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0"/>
+      <c r="D17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0"/>
+      <c r="D18" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -530,4 +580,233 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>46025</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>46026</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F13" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/data-visualization/power-bi/examples/sorting-tables/data2/prod_db.xlsx
+++ b/data-visualization/power-bi/examples/sorting-tables/data2/prod_db.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="fruits_db" sheetId="1" state="visible" r:id="rId3"/>
@@ -353,17 +353,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="12.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="16.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16379" min="16378" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16380" style="0" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -382,11 +380,6 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0"/>
-      <c r="G1" s="0"/>
-      <c r="H1" s="0"/>
-      <c r="I1" s="0"/>
-      <c r="J1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -404,11 +397,6 @@
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="0"/>
-      <c r="G2" s="0"/>
-      <c r="H2" s="0"/>
-      <c r="I2" s="0"/>
-      <c r="J2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
@@ -426,11 +414,6 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="0"/>
-      <c r="G3" s="0"/>
-      <c r="H3" s="0"/>
-      <c r="I3" s="0"/>
-      <c r="J3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
@@ -448,11 +431,6 @@
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="0"/>
-      <c r="G4" s="0"/>
-      <c r="H4" s="0"/>
-      <c r="I4" s="0"/>
-      <c r="J4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -470,11 +448,6 @@
       <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="0"/>
-      <c r="G5" s="0"/>
-      <c r="H5" s="0"/>
-      <c r="I5" s="0"/>
-      <c r="J5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -530,7 +503,6 @@
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="E9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
@@ -539,38 +511,14 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0"/>
-      <c r="D11" s="0"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0"/>
-      <c r="D12" s="0"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0"/>
-      <c r="D13" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0"/>
-      <c r="D14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0"/>
-      <c r="D15" s="0"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0"/>
-      <c r="D16" s="0"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0"/>
-      <c r="D17" s="0"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0"/>
-      <c r="D18" s="0"/>
-    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -590,7 +538,7 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -609,7 +557,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -629,7 +577,7 @@
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -649,7 +597,7 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -669,7 +617,7 @@
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -689,7 +637,7 @@
       <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.9</v>
       </c>
     </row>
